--- a/data/trans_dic/P16A_n_R3-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P16A_n_R3-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido cinco o más medicamentos en las dos últimas semanas</t>
+          <t>Población que ha consumido cinco o más medicamentos en las dos últimas semanas (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -722,57 +722,57 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,65; 5,27</t>
+          <t>0,67; 5,32</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,82; 3,7</t>
+          <t>0,68; 3,66</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,97; 3,87</t>
+          <t>1,04; 4,04</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,22; 5,76</t>
+          <t>1,22; 5,64</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,35; 5,39</t>
+          <t>1,34; 4,98</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,74; 5,79</t>
+          <t>1,59; 6,05</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,49; 5,78</t>
+          <t>2,48; 5,87</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,88; 3,25</t>
+          <t>0,78; 3,26</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,22; 4,37</t>
+          <t>1,49; 4,35</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,49; 4,02</t>
+          <t>1,41; 4,13</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,02; 4,25</t>
+          <t>2,09; 4,25</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,41; 2,61</t>
+          <t>0,43; 2,67</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,14; 6,35</t>
+          <t>2,28; 6,55</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,75; 2,91</t>
+          <t>0,74; 2,98</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,3; 5,9</t>
+          <t>2,09; 5,83</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,47; 5,88</t>
+          <t>2,6; 5,81</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,64; 9,2</t>
+          <t>4,43; 8,95</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,0; 5,32</t>
+          <t>1,99; 5,28</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,89; 9,62</t>
+          <t>5,78; 9,48</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,77; 3,71</t>
+          <t>1,81; 3,73</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3,89; 6,76</t>
+          <t>3,9; 6,87</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,59; 3,77</t>
+          <t>1,55; 3,65</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,39; 7,07</t>
+          <t>4,48; 7,2</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,8</t>
+          <t>0,0; 1,69</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,89</t>
+          <t>0,0; 1,76</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,59</t>
+          <t>0,0; 1,74</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,91; 9,89</t>
+          <t>5,03; 10,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,61; 3,47</t>
+          <t>0,6; 3,67</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,83; 4,05</t>
+          <t>0,77; 3,91</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11,05; 16,48</t>
+          <t>10,94; 16,61</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,87</t>
+          <t>0,0; 0,73</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,33; 2,03</t>
+          <t>0,33; 1,94</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,57; 2,43</t>
+          <t>0,59; 2,38</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8,77; 12,67</t>
+          <t>8,58; 12,39</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,23; 1,93</t>
+          <t>0,24; 2,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,32; 3,0</t>
+          <t>0,31; 2,88</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,24; 4,32</t>
+          <t>1,21; 4,18</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,66; 8,75</t>
+          <t>3,6; 8,86</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,84; 3,9</t>
+          <t>0,98; 3,95</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,63; 11,1</t>
+          <t>5,54; 10,88</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,99; 10,21</t>
+          <t>5,08; 10,68</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,6; 8,45</t>
+          <t>3,78; 8,38</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,77; 2,47</t>
+          <t>0,75; 2,47</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,17; 6,28</t>
+          <t>3,19; 6,35</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,53; 6,76</t>
+          <t>3,48; 6,73</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,15; 7,62</t>
+          <t>4,29; 7,74</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,03</t>
+          <t>0,0; 2,42</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,02; 7,92</t>
+          <t>2,11; 8,51</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,38; 3,74</t>
+          <t>0,38; 3,87</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,14; 9,63</t>
+          <t>4,31; 10,05</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,48; 4,47</t>
+          <t>0,48; 5,28</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,39; 20,25</t>
+          <t>9,91; 20,27</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,4; 8,6</t>
+          <t>2,47; 8,91</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>5,67; 14,83</t>
+          <t>5,89; 14,96</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,46; 2,65</t>
+          <t>0,44; 2,6</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7,02; 12,7</t>
+          <t>7,02; 13,23</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,74; 5,3</t>
+          <t>1,8; 5,05</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,41; 11,6</t>
+          <t>6,28; 11,58</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,98</t>
+          <t>0,0; 2,07</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,62</t>
+          <t>0,0; 2,57</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,01; 5,04</t>
+          <t>1,04; 4,99</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7,59; 13,09</t>
+          <t>7,86; 13,26</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,91</t>
+          <t>0,33; 3,08</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,05; 4,7</t>
+          <t>1,06; 4,89</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,68; 9,99</t>
+          <t>3,56; 9,75</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>10,18; 16,06</t>
+          <t>10,35; 16,09</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,33; 1,92</t>
+          <t>0,33; 2,09</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,72; 2,78</t>
+          <t>0,58; 2,82</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2,76; 6,55</t>
+          <t>2,7; 6,61</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>9,62; 13,66</t>
+          <t>9,78; 13,75</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,15; 3,81</t>
+          <t>1,15; 3,65</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,66; 2,9</t>
+          <t>0,75; 2,85</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,45; 4,15</t>
+          <t>1,45; 4,16</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,1; 4,76</t>
+          <t>2,2; 4,67</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,06; 3,03</t>
+          <t>1,17; 3,34</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,71; 4,22</t>
+          <t>1,74; 4,37</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,98; 4,74</t>
+          <t>1,99; 4,93</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,93; 10,98</t>
+          <t>3,48; 11,13</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,39; 2,96</t>
+          <t>1,4; 2,95</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,41; 3,09</t>
+          <t>1,47; 3,17</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2,01; 4,03</t>
+          <t>1,96; 3,9</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3,73; 7,38</t>
+          <t>3,53; 7,55</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,85; 4,46</t>
+          <t>1,85; 4,31</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,43; 2,27</t>
+          <t>0,42; 2,21</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,34; 1,77</t>
+          <t>0,26; 1,77</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,36; 5,08</t>
+          <t>1,48; 5,08</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,86; 5,7</t>
+          <t>2,81; 5,75</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,61; 6,96</t>
+          <t>3,62; 7,05</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,61; 6,87</t>
+          <t>3,75; 7,1</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>8,44; 12,84</t>
+          <t>8,38; 12,43</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2,61; 4,66</t>
+          <t>2,49; 4,4</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2,25; 4,21</t>
+          <t>2,34; 4,29</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2,24; 4,12</t>
+          <t>2,18; 4,0</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>3,83; 7,95</t>
+          <t>3,75; 7,95</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,12; 1,97</t>
+          <t>1,12; 1,92</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,34; 2,35</t>
+          <t>1,36; 2,37</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,27; 2,09</t>
+          <t>1,25; 2,1</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3,57; 5,31</t>
+          <t>3,54; 5,25</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2,05; 3,2</t>
+          <t>2,11; 3,18</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,33; 5,77</t>
+          <t>4,28; 5,73</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,6; 5,04</t>
+          <t>3,67; 5,17</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>7,12; 9,81</t>
+          <t>7,17; 9,86</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,71; 2,42</t>
+          <t>1,71; 2,4</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2,95; 3,88</t>
+          <t>3,01; 3,9</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2,58; 3,46</t>
+          <t>2,62; 3,49</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>5,88; 7,48</t>
+          <t>5,79; 7,44</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido cinco o más medicamentos en las dos últimas semanas</t>
+          <t>Población que ha consumido cinco o más medicamentos en las dos últimas semanas (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 5212</t>
+          <t>0; 5210</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1901; 15541</t>
+          <t>1968; 15689</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2408; 10858</t>
+          <t>1992; 10765</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3016; 12041</t>
+          <t>3228; 12573</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3179; 15022</t>
+          <t>3173; 14717</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3892; 15473</t>
+          <t>3860; 14307</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5017; 16721</t>
+          <t>4585; 17477</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>7223; 16728</t>
+          <t>7193; 16999</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>4687; 17344</t>
+          <t>4149; 17422</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7117; 25409</t>
+          <t>8658; 25323</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8696; 23418</t>
+          <t>8211; 24073</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>12145; 25554</t>
+          <t>12553; 25553</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2027; 12858</t>
+          <t>2131; 13178</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10833; 32108</t>
+          <t>11527; 33129</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3751; 14629</t>
+          <t>3730; 14975</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11900; 30597</t>
+          <t>10850; 30220</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>12451; 29656</t>
+          <t>13085; 29296</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>24299; 48202</t>
+          <t>23223; 46879</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10474; 27843</t>
+          <t>10396; 27638</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>30320; 49546</t>
+          <t>29766; 48826</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>17688; 37021</t>
+          <t>18073; 37173</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>40077; 69602</t>
+          <t>40164; 70724</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>16271; 38646</t>
+          <t>15904; 37418</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>45366; 73050</t>
+          <t>46308; 74409</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 5743</t>
+          <t>0; 5379</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 6134</t>
+          <t>0; 5691</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 5066</t>
+          <t>0; 5550</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>15520; 31245</t>
+          <t>15891; 31606</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 1916</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2065; 11849</t>
+          <t>2058; 12520</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2797; 13622</t>
+          <t>2586; 13158</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>38569; 57537</t>
+          <t>38200; 57995</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 5690</t>
+          <t>0; 4780</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2195; 13511</t>
+          <t>2177; 12925</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3745; 15930</t>
+          <t>3835; 15611</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>58343; 84295</t>
+          <t>57067; 82391</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>838; 6927</t>
+          <t>845; 7190</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1185; 11201</t>
+          <t>1159; 10771</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4602; 16000</t>
+          <t>4494; 15478</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>11430; 27347</t>
+          <t>11244; 27688</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3126; 14502</t>
+          <t>3656; 14680</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>21888; 43162</t>
+          <t>21558; 42329</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>19319; 39530</t>
+          <t>19655; 41381</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>17129; 40217</t>
+          <t>18006; 39845</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5601; 18053</t>
+          <t>5509; 18011</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>24184; 47912</t>
+          <t>24338; 48442</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>26695; 51216</t>
+          <t>26356; 50949</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>32704; 60043</t>
+          <t>33836; 60993</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 4128</t>
+          <t>0; 4912</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>4288; 16844</t>
+          <t>4483; 18089</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>805; 7897</t>
+          <t>810; 8175</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7398; 17216</t>
+          <t>7711; 17958</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>992; 9278</t>
+          <t>1002; 10958</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>22817; 44462</t>
+          <t>21754; 44522</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5253; 18795</t>
+          <t>5390; 19483</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>14678; 38368</t>
+          <t>15234; 38711</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1874; 10896</t>
+          <t>1816; 10700</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>30340; 54896</t>
+          <t>30324; 57171</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>7476; 22776</t>
+          <t>7733; 21701</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>28052; 50736</t>
+          <t>27494; 50656</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 5371</t>
+          <t>0; 5594</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 7178</t>
+          <t>0; 7034</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2645; 13251</t>
+          <t>2743; 13126</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>20452; 35288</t>
+          <t>21183; 35766</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>901; 8082</t>
+          <t>906; 8577</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2948; 13161</t>
+          <t>2973; 13704</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>10044; 27295</t>
+          <t>9721; 26622</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>26161; 41277</t>
+          <t>26598; 41368</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1828; 10531</t>
+          <t>1839; 11478</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>4010; 15387</t>
+          <t>3198; 15610</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>14796; 35142</t>
+          <t>14503; 35461</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>50666; 71939</t>
+          <t>51504; 72443</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>7090; 23415</t>
+          <t>7042; 22455</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>4407; 19206</t>
+          <t>4950; 18876</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>9500; 27250</t>
+          <t>9488; 27283</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>13140; 29710</t>
+          <t>13731; 29155</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>6790; 19353</t>
+          <t>7457; 21311</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>11832; 29277</t>
+          <t>12078; 30325</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13668; 32748</t>
+          <t>13758; 34097</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>33367; 93272</t>
+          <t>29527; 94562</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>17442; 37101</t>
+          <t>17488; 37024</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>19086; 41913</t>
+          <t>19924; 43053</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>27114; 54363</t>
+          <t>26452; 52514</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>55001; 108801</t>
+          <t>52012; 111206</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>13789; 33203</t>
+          <t>13767; 32057</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3331; 17704</t>
+          <t>3241; 17190</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2677; 13792</t>
+          <t>2026; 13772</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>12655; 47148</t>
+          <t>13714; 47172</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>22384; 44642</t>
+          <t>22038; 45020</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>29733; 57379</t>
+          <t>29863; 58093</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>29844; 56764</t>
+          <t>30969; 58685</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>60546; 92158</t>
+          <t>60111; 89217</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>39818; 71210</t>
+          <t>37999; 67235</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>36073; 67498</t>
+          <t>37491; 68843</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>35915; 66158</t>
+          <t>34970; 64220</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>63085; 130889</t>
+          <t>61706; 130954</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>36592; 64528</t>
+          <t>36732; 62924</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>45861; 80691</t>
+          <t>46500; 81122</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>43049; 70937</t>
+          <t>42439; 71332</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>123430; 183887</t>
+          <t>122552; 181536</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>69379; 108246</t>
+          <t>71158; 107516</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>154178; 205263</t>
+          <t>152290; 203778</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>127474; 178651</t>
+          <t>130043; 183207</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>264499; 364092</t>
+          <t>266250; 365936</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>113981; 161115</t>
+          <t>113739; 160060</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>205742; 271287</t>
+          <t>210195; 272328</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>179161; 239935</t>
+          <t>181738; 242032</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>421523; 536767</t>
+          <t>415423; 533785</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P16A_n_R3-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P16A_n_R3-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,88%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,91</t>
+          <t>0,0; 2,17</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,67; 5,32</t>
+          <t>0,94; 5,36</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,68; 3,66</t>
+          <t>0,81; 3,99</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,04; 4,04</t>
+          <t>0,96; 3,92</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,22; 5,64</t>
+          <t>1,25; 5,86</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,34; 4,98</t>
+          <t>1,32; 5,16</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,59; 6,05</t>
+          <t>1,47; 5,82</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,48; 5,87</t>
+          <t>2,27; 5,5</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,78; 3,26</t>
+          <t>0,84; 3,06</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,49; 4,35</t>
+          <t>1,36; 4,32</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,41; 4,13</t>
+          <t>1,51; 3,98</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,09; 4,25</t>
+          <t>1,92; 4,03</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,52%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,43; 2,67</t>
+          <t>0,43; 2,49</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,28; 6,55</t>
+          <t>2,1; 6,31</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,74; 2,98</t>
+          <t>0,63; 2,88</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,09; 5,83</t>
+          <t>2,24; 5,66</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,6; 5,81</t>
+          <t>2,42; 6,03</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,43; 8,95</t>
+          <t>4,58; 9,07</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,99; 5,28</t>
+          <t>1,99; 5,21</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,78; 9,48</t>
+          <t>5,67; 9,24</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,81; 3,73</t>
+          <t>1,65; 3,66</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3,9; 6,87</t>
+          <t>3,81; 7,1</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,55; 3,65</t>
+          <t>1,56; 3,63</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,48; 7,2</t>
+          <t>4,37; 7,02</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,44%</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,69</t>
+          <t>0,0; 1,64</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,76</t>
+          <t>0,0; 1,79</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,03; 10,0</t>
+          <t>4,86; 9,96</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1022,17 +1022,17 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,6; 3,67</t>
+          <t>0,62; 3,72</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,77; 3,91</t>
+          <t>0,76; 4,21</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10,94; 16,61</t>
+          <t>11,07; 16,8</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1042,17 +1042,17 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,33; 1,94</t>
+          <t>0,32; 1,9</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,59; 2,38</t>
+          <t>0,56; 2,32</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8,58; 12,39</t>
+          <t>8,62; 12,45</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,36%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,0</t>
+          <t>0,23; 2,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,31; 2,88</t>
+          <t>0,31; 3,1</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,21; 4,18</t>
+          <t>1,21; 4,17</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,6; 8,86</t>
+          <t>3,44; 7,87</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,98; 3,95</t>
+          <t>1,08; 4,35</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,54; 10,88</t>
+          <t>5,7; 10,98</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,08; 10,68</t>
+          <t>5,07; 10,88</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,78; 8,38</t>
+          <t>5,78; 9,35</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,75; 2,47</t>
+          <t>0,79; 2,57</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,19; 6,35</t>
+          <t>3,21; 6,45</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,48; 6,73</t>
+          <t>3,66; 6,81</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,29; 7,74</t>
+          <t>5,01; 7,97</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,62%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,42</t>
+          <t>0,0; 2,32</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,11; 8,51</t>
+          <t>2,01; 7,85</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,38; 3,87</t>
+          <t>0,38; 3,77</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,31; 10,05</t>
+          <t>3,7; 8,39</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,48; 5,28</t>
+          <t>0,59; 4,94</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,91; 20,27</t>
+          <t>10,12; 19,49</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,47; 8,91</t>
+          <t>2,39; 8,41</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>5,89; 14,96</t>
+          <t>10,37; 15,98</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,44; 2,6</t>
+          <t>0,45; 2,77</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7,02; 13,23</t>
+          <t>6,9; 12,64</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,8; 5,05</t>
+          <t>1,61; 4,93</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,28; 11,58</t>
+          <t>7,97; 11,73</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,53%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,07</t>
+          <t>0,0; 2,29</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,57</t>
+          <t>0,0; 2,6</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,04; 4,99</t>
+          <t>0,99; 4,87</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7,86; 13,26</t>
+          <t>7,54; 13,08</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,33; 3,08</t>
+          <t>0,33; 2,91</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,06; 4,89</t>
+          <t>0,77; 4,62</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,56; 9,75</t>
+          <t>3,62; 10,17</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>10,35; 16,09</t>
+          <t>10,6; 16,42</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,33; 2,09</t>
+          <t>0,32; 1,97</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,58; 2,82</t>
+          <t>0,73; 2,95</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2,7; 6,61</t>
+          <t>2,76; 6,41</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>9,78; 13,75</t>
+          <t>9,65; 13,5</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>7,24%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,15; 3,65</t>
+          <t>1,15; 3,57</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,75; 2,85</t>
+          <t>0,74; 2,82</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,45; 4,16</t>
+          <t>1,44; 4,2</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,2; 4,67</t>
+          <t>2,22; 4,97</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,17; 3,34</t>
+          <t>1,09; 3,3</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,74; 4,37</t>
+          <t>1,71; 4,36</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,99; 4,93</t>
+          <t>1,94; 4,94</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,48; 11,13</t>
+          <t>9,14; 12,89</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,4; 2,95</t>
+          <t>1,38; 2,97</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,47; 3,17</t>
+          <t>1,47; 3,11</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,96; 3,9</t>
+          <t>2,12; 3,99</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3,53; 7,55</t>
+          <t>6,21; 8,48</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>7,0%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,85; 4,31</t>
+          <t>1,89; 4,32</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,42; 2,21</t>
+          <t>0,38; 2,17</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,26; 1,77</t>
+          <t>0,31; 1,71</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,48; 5,08</t>
+          <t>3,36; 5,81</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,81; 5,75</t>
+          <t>2,67; 5,68</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,62; 7,05</t>
+          <t>3,66; 6,89</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,75; 7,1</t>
+          <t>3,64; 6,98</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>8,38; 12,43</t>
+          <t>7,83; 11,23</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2,49; 4,4</t>
+          <t>2,61; 4,5</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2,34; 4,29</t>
+          <t>2,27; 4,1</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2,18; 4,0</t>
+          <t>2,14; 3,99</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>3,75; 7,95</t>
+          <t>6,01; 8,17</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>7,21%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,12; 1,92</t>
+          <t>1,12; 2,02</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,36; 2,37</t>
+          <t>1,36; 2,48</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,25; 2,1</t>
+          <t>1,23; 2,12</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3,54; 5,25</t>
+          <t>4,15; 5,39</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2,11; 3,18</t>
+          <t>2,1; 3,23</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,28; 5,73</t>
+          <t>4,26; 5,77</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,67; 5,17</t>
+          <t>3,66; 5,01</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>7,17; 9,86</t>
+          <t>8,86; 10,45</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,71; 2,4</t>
+          <t>1,72; 2,39</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3,01; 3,9</t>
+          <t>3,0; 3,87</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2,62; 3,49</t>
+          <t>2,63; 3,48</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>5,79; 7,44</t>
+          <t>6,72; 7,72</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6581</t>
+          <t>6883</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>11396</t>
+          <t>11421</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>17977</t>
+          <t>18304</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 5210</t>
+          <t>0; 5919</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1968; 15689</t>
+          <t>2776; 15788</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1992; 10765</t>
+          <t>2368; 11728</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3228; 12573</t>
+          <t>3046; 12506</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3173; 14717</t>
+          <t>3263; 15272</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3860; 14307</t>
+          <t>3782; 14821</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4585; 17477</t>
+          <t>4234; 16803</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>7193; 16999</t>
+          <t>7185; 17397</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>4149; 17422</t>
+          <t>4502; 16328</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>8658; 25323</t>
+          <t>7937; 25139</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8211; 24073</t>
+          <t>8814; 23198</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>12553; 25553</t>
+          <t>12206; 25575</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>18979</t>
+          <t>19511</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>38680</t>
+          <t>40000</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>57659</t>
+          <t>59511</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2131; 13178</t>
+          <t>2126; 12264</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11527; 33129</t>
+          <t>10640; 31892</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3730; 14975</t>
+          <t>3168; 14472</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10850; 30220</t>
+          <t>11887; 30030</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>13085; 29296</t>
+          <t>12197; 30406</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>23223; 46879</t>
+          <t>23994; 47519</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10396; 27638</t>
+          <t>10394; 27273</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>29766; 48826</t>
+          <t>30975; 50501</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>18073; 37173</t>
+          <t>16495; 36538</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>40164; 70724</t>
+          <t>39174; 73066</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>15904; 37418</t>
+          <t>15979; 37226</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>46308; 74409</t>
+          <t>47125; 75603</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>22445</t>
+          <t>22051</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>47448</t>
+          <t>48175</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>69893</t>
+          <t>70226</t>
         </is>
       </c>
     </row>
@@ -2625,22 +2625,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 5379</t>
+          <t>0; 5233</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 5691</t>
+          <t>0; 5791</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 5550</t>
+          <t>0; 5548</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>15891; 31606</t>
+          <t>15345; 31485</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -2650,37 +2650,37 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2058; 12520</t>
+          <t>2098; 12674</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2586; 13158</t>
+          <t>2571; 14151</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>38200; 57995</t>
+          <t>39438; 59887</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 4780</t>
+          <t>0; 4759</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2177; 12925</t>
+          <t>2141; 12654</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3835; 15611</t>
+          <t>3679; 15192</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>57067; 82391</t>
+          <t>57971; 83689</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>17779</t>
+          <t>19740</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>29034</t>
+          <t>30800</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>46813</t>
+          <t>50540</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>845; 7190</t>
+          <t>834; 7172</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1159; 10771</t>
+          <t>1176; 11583</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4494; 15478</t>
+          <t>4464; 15416</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>11244; 27688</t>
+          <t>12842; 29384</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3656; 14680</t>
+          <t>3999; 16174</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>21558; 42329</t>
+          <t>22157; 42710</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>19655; 41381</t>
+          <t>19637; 42143</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>18006; 39845</t>
+          <t>24398; 39456</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5509; 18011</t>
+          <t>5763; 18787</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>24338; 48442</t>
+          <t>24470; 49215</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>26356; 50949</t>
+          <t>27751; 51583</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>33836; 60993</t>
+          <t>39872; 63363</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11339</t>
+          <t>11806</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>29020</t>
+          <t>29995</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>40359</t>
+          <t>41800</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 4912</t>
+          <t>0; 4707</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>4483; 18089</t>
+          <t>4276; 16698</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>810; 8175</t>
+          <t>804; 7967</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7711; 17958</t>
+          <t>7619; 17249</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1002; 10958</t>
+          <t>1216; 10256</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>21754; 44522</t>
+          <t>22231; 42796</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5390; 19483</t>
+          <t>5218; 18385</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>15234; 38711</t>
+          <t>23739; 36575</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1816; 10700</t>
+          <t>1869; 11381</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>30324; 57171</t>
+          <t>29830; 54651</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>7733; 21701</t>
+          <t>6934; 21183</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>27494; 50656</t>
+          <t>34617; 50981</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>27435</t>
+          <t>27065</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>33353</t>
+          <t>34555</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>60788</t>
+          <t>61621</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 5594</t>
+          <t>0; 6213</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 7034</t>
+          <t>0; 7116</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2743; 13126</t>
+          <t>2595; 12825</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>21183; 35766</t>
+          <t>20402; 35408</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>906; 8577</t>
+          <t>906; 8101</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2973; 13704</t>
+          <t>2167; 12926</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>9721; 26622</t>
+          <t>9892; 27768</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>26598; 41368</t>
+          <t>27969; 43316</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1839; 11478</t>
+          <t>1749; 10821</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3198; 15610</t>
+          <t>4059; 16320</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>14503; 35461</t>
+          <t>14776; 34399</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>51504; 72443</t>
+          <t>51578; 72157</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>20550</t>
+          <t>24615</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>68149</t>
+          <t>83423</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>88699</t>
+          <t>108038</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>7042; 22455</t>
+          <t>7087; 21968</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>4950; 18876</t>
+          <t>4902; 18714</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>9488; 27283</t>
+          <t>9460; 27605</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>13731; 29155</t>
+          <t>15986; 35767</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>7457; 21311</t>
+          <t>6950; 21062</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>12078; 30325</t>
+          <t>11869; 30265</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13758; 34097</t>
+          <t>13412; 34138</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>29527; 94562</t>
+          <t>70600; 99547</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>17488; 37024</t>
+          <t>17272; 37270</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>19924; 43053</t>
+          <t>19909; 42134</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>26452; 52514</t>
+          <t>28580; 53802</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>52012; 111206</t>
+          <t>92674; 126499</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>31430</t>
+          <t>35744</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>72724</t>
+          <t>78244</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>104154</t>
+          <t>113988</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>13767; 32057</t>
+          <t>14087; 32147</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3241; 17190</t>
+          <t>2992; 16907</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2026; 13772</t>
+          <t>2375; 13287</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>13714; 47172</t>
+          <t>26797; 46403</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>22038; 45020</t>
+          <t>20902; 44465</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>29863; 58093</t>
+          <t>30158; 56733</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>30969; 58685</t>
+          <t>30061; 57694</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>60111; 89217</t>
+          <t>65083; 93353</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>37999; 67235</t>
+          <t>39826; 68684</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>37491; 68843</t>
+          <t>36364; 65668</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>34970; 64220</t>
+          <t>34388; 64002</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>61706; 130954</t>
+          <t>97906; 133178</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>156537</t>
+          <t>167415</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>329805</t>
+          <t>356614</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>486342</t>
+          <t>524028</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>36732; 62924</t>
+          <t>36699; 66042</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>46500; 81122</t>
+          <t>46738; 84898</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>42439; 71332</t>
+          <t>41897; 72025</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>122552; 181536</t>
+          <t>146648; 190405</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>71158; 107516</t>
+          <t>71073; 109134</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>152290; 203778</t>
+          <t>151751; 205189</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>130043; 183207</t>
+          <t>129772; 177696</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>266250; 365936</t>
+          <t>331277; 390470</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>113739; 160060</t>
+          <t>114323; 159065</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>210195; 272328</t>
+          <t>209642; 270618</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>181738; 242032</t>
+          <t>182546; 241787</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>415423; 533785</t>
+          <t>488369; 561122</t>
         </is>
       </c>
     </row>
